--- a/kronshtatsky/walls/walls-k.xlsx
+++ b/kronshtatsky/walls/walls-k.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="120" yWindow="12" windowWidth="12096" windowHeight="6348" tabRatio="766" firstSheet="39" activeTab="45"/>
+    <workbookView xWindow="120" yWindow="12" windowWidth="12096" windowHeight="6348" tabRatio="766" firstSheet="39" activeTab="43"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -42615,7 +42615,7 @@
       </c>
       <c r="E4" s="157">
         <f ca="1">B4-RANDBETWEEN(2, 5)-RANDBETWEEN(1,10)/10</f>
-        <v>80.600000000000009</v>
+        <v>80.2</v>
       </c>
       <c r="G4" s="147">
         <v>89.4</v>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="E5" s="157">
         <f t="shared" ref="E5:E31" ca="1" si="0">B5-RANDBETWEEN(2, 5)-RANDBETWEEN(1,10)/10</f>
-        <v>125.29999999999998</v>
+        <v>126.69999999999999</v>
       </c>
       <c r="G5" s="147">
         <v>133.5</v>
@@ -42645,7 +42645,7 @@
       </c>
       <c r="E6" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>356.7</v>
+        <v>356.9</v>
       </c>
       <c r="G6" s="147">
         <v>367.5</v>
@@ -42660,7 +42660,7 @@
       </c>
       <c r="E7" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>121.50000000000001</v>
+        <v>121.30000000000001</v>
       </c>
       <c r="G7" s="147">
         <v>131.30000000000001</v>
@@ -42675,7 +42675,7 @@
       </c>
       <c r="E8" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>56.800000000000004</v>
+        <v>55.7</v>
       </c>
       <c r="G8" s="147">
         <v>67.400000000000006</v>
@@ -42690,7 +42690,7 @@
       </c>
       <c r="E9" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>122.6</v>
+        <v>124.29999999999998</v>
       </c>
       <c r="G9" s="147">
         <v>129.69999999999999</v>
@@ -42705,7 +42705,7 @@
       </c>
       <c r="E10" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>88.2</v>
+        <v>87.2</v>
       </c>
       <c r="G10" s="147">
         <v>95.8</v>
@@ -42720,7 +42720,7 @@
       </c>
       <c r="E11" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>59.900000000000006</v>
+        <v>59.5</v>
       </c>
       <c r="G11" s="147">
         <v>67.400000000000006</v>
@@ -42735,7 +42735,7 @@
       </c>
       <c r="E12" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>297.10000000000002</v>
+        <v>299.20000000000005</v>
       </c>
       <c r="G12" s="147">
         <v>305.5</v>
@@ -42750,7 +42750,7 @@
       </c>
       <c r="E13" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>410.5</v>
+        <v>410.6</v>
       </c>
       <c r="G13" s="147">
         <v>419</v>
@@ -42765,7 +42765,7 @@
       </c>
       <c r="E14" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>91.4</v>
+        <v>92</v>
       </c>
       <c r="G14" s="147">
         <v>98.3</v>
@@ -42780,7 +42780,7 @@
       </c>
       <c r="E15" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>106.5</v>
+        <v>107.5</v>
       </c>
       <c r="G15" s="147">
         <v>115.3</v>
@@ -42795,7 +42795,7 @@
       </c>
       <c r="E16" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>63.500000000000007</v>
+        <v>64.600000000000009</v>
       </c>
       <c r="G16" s="147">
         <v>70.400000000000006</v>
@@ -42810,7 +42810,7 @@
       </c>
       <c r="E17" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>213.2</v>
+        <v>213.1</v>
       </c>
       <c r="G17" s="147">
         <v>223.7</v>
@@ -42825,7 +42825,7 @@
       </c>
       <c r="E18" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>35.5</v>
+        <v>38.5</v>
       </c>
       <c r="G18" s="147">
         <v>45.2</v>
@@ -42840,7 +42840,7 @@
       </c>
       <c r="E19" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>38.199999999999996</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="G19" s="147">
         <v>42.4</v>
@@ -42855,7 +42855,7 @@
       </c>
       <c r="E20" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>71.5</v>
+        <v>70</v>
       </c>
       <c r="G20" s="147">
         <v>79.099999999999994</v>
@@ -42870,7 +42870,7 @@
       </c>
       <c r="E21" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>85.8</v>
+        <v>85.3</v>
       </c>
       <c r="G21" s="147">
         <v>94.2</v>
@@ -42885,7 +42885,7 @@
       </c>
       <c r="E22" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>81.599999999999994</v>
+        <v>82.1</v>
       </c>
       <c r="G22" s="147">
         <v>89.7</v>
@@ -42900,7 +42900,7 @@
       </c>
       <c r="E23" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>456.8</v>
+        <v>457.6</v>
       </c>
       <c r="G23" s="147">
         <v>464.7</v>
@@ -42915,7 +42915,7 @@
       </c>
       <c r="E24" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>331.5</v>
+        <v>334.20000000000005</v>
       </c>
       <c r="G24" s="147">
         <v>342.8</v>
@@ -42930,7 +42930,7 @@
       </c>
       <c r="E25" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>65.2</v>
+        <v>62</v>
       </c>
       <c r="G25" s="147">
         <v>73.5</v>
@@ -42945,7 +42945,7 @@
       </c>
       <c r="E26" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>135.5</v>
+        <v>133.4</v>
       </c>
       <c r="G26" s="147">
         <v>142.30000000000001</v>
@@ -42960,7 +42960,7 @@
       </c>
       <c r="E27" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>108.00000000000001</v>
+        <v>109.2</v>
       </c>
       <c r="G27" s="147">
         <v>118.9</v>
@@ -42975,7 +42975,7 @@
       </c>
       <c r="E28" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>296.3</v>
+        <v>296.5</v>
       </c>
       <c r="G28" s="147">
         <v>304.3</v>
@@ -42990,7 +42990,7 @@
       </c>
       <c r="E29" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>388.29999999999995</v>
+        <v>387.49999999999994</v>
       </c>
       <c r="G29" s="147">
         <v>395.7</v>
@@ -43005,7 +43005,7 @@
       </c>
       <c r="E30" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>184.00000000000003</v>
+        <v>183.60000000000002</v>
       </c>
       <c r="G30" s="147">
         <v>190.8</v>
@@ -43020,7 +43020,7 @@
       </c>
       <c r="E31" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>217.8</v>
+        <v>217.4</v>
       </c>
       <c r="G31" s="147">
         <v>227.1</v>
@@ -43082,7 +43082,7 @@
       </c>
       <c r="E5" s="157">
         <f ca="1">B5-RANDBETWEEN(2, 5)-RANDBETWEEN(1,10)/10</f>
-        <v>8.1</v>
+        <v>5.1000000000000005</v>
       </c>
       <c r="F5" s="157"/>
       <c r="G5" s="147">
@@ -43098,7 +43098,7 @@
       </c>
       <c r="E6" s="157">
         <f t="shared" ref="E6:E69" ca="1" si="0">B6-RANDBETWEEN(2, 5)-RANDBETWEEN(1,10)/10</f>
-        <v>21.5</v>
+        <v>23.5</v>
       </c>
       <c r="G6" s="147">
         <v>32.9</v>
@@ -43113,7 +43113,7 @@
       </c>
       <c r="E7" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>20.700000000000003</v>
+        <v>19.8</v>
       </c>
       <c r="G7" s="147">
         <v>27.1</v>
@@ -43128,7 +43128,7 @@
       </c>
       <c r="E8" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>434.7</v>
+        <v>434.2</v>
       </c>
       <c r="G8" s="147">
         <v>444.7</v>
@@ -43143,7 +43143,7 @@
       </c>
       <c r="E9" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
       <c r="G9" s="147">
         <v>68.7</v>
@@ -43158,7 +43158,7 @@
       </c>
       <c r="E10" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>26.9</v>
+        <v>27.3</v>
       </c>
       <c r="G10" s="147">
         <v>36.5</v>
@@ -43173,7 +43173,7 @@
       </c>
       <c r="E11" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>40.500000000000007</v>
+        <v>38.300000000000004</v>
       </c>
       <c r="G11" s="147">
         <v>46.7</v>
@@ -43188,7 +43188,7 @@
       </c>
       <c r="E12" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G12" s="147">
         <v>155.5</v>
@@ -43203,7 +43203,7 @@
       </c>
       <c r="E13" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>109.99999999999999</v>
+        <v>108.49999999999999</v>
       </c>
       <c r="G13" s="147">
         <v>118.6</v>
@@ -43218,7 +43218,7 @@
       </c>
       <c r="E14" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>102</v>
+        <v>101.4</v>
       </c>
       <c r="G14" s="147">
         <v>109.5</v>
@@ -43233,7 +43233,7 @@
       </c>
       <c r="E15" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>102.2</v>
+        <v>104.10000000000001</v>
       </c>
       <c r="G15" s="147">
         <v>112.7</v>
@@ -43248,7 +43248,7 @@
       </c>
       <c r="E16" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>165.9</v>
+        <v>164.1</v>
       </c>
       <c r="G16" s="147">
         <v>174.2</v>
@@ -43263,7 +43263,7 @@
       </c>
       <c r="E17" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>73.5</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="G17" s="147">
         <v>80.2</v>
@@ -43278,7 +43278,7 @@
       </c>
       <c r="E18" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>26.699999999999996</v>
+        <v>27.399999999999995</v>
       </c>
       <c r="G18" s="147">
         <v>34.799999999999997</v>
@@ -43293,7 +43293,7 @@
       </c>
       <c r="E19" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>71.7</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="G19" s="147">
         <v>80.3</v>
@@ -43308,7 +43308,7 @@
       </c>
       <c r="E20" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="G20" s="147">
         <v>22.7</v>
@@ -43323,7 +43323,7 @@
       </c>
       <c r="E21" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>50.8</v>
+        <v>51.4</v>
       </c>
       <c r="G21" s="147">
         <v>59.4</v>
@@ -43338,7 +43338,7 @@
       </c>
       <c r="E22" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>52.7</v>
+        <v>51.4</v>
       </c>
       <c r="G22" s="147">
         <v>58</v>
@@ -43353,7 +43353,7 @@
       </c>
       <c r="E23" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>57.2</v>
+        <v>57.800000000000004</v>
       </c>
       <c r="G23" s="147">
         <v>67.2</v>
@@ -43368,7 +43368,7 @@
       </c>
       <c r="E24" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>36.400000000000006</v>
+        <v>36.500000000000007</v>
       </c>
       <c r="G24" s="147">
         <v>43.7</v>
@@ -43383,7 +43383,7 @@
       </c>
       <c r="E25" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="G25" s="147">
         <v>33</v>
@@ -43398,7 +43398,7 @@
       </c>
       <c r="E26" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>33.4</v>
+        <v>31.9</v>
       </c>
       <c r="G26" s="147">
         <v>42.9</v>
@@ -43413,7 +43413,7 @@
       </c>
       <c r="E27" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>45.199999999999996</v>
+        <v>45.599999999999994</v>
       </c>
       <c r="G27" s="147">
         <v>51.3</v>
@@ -43428,7 +43428,7 @@
       </c>
       <c r="E28" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>41.800000000000004</v>
+        <v>43.400000000000006</v>
       </c>
       <c r="G28" s="147">
         <v>50.7</v>
@@ -43443,7 +43443,7 @@
       </c>
       <c r="E29" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>51.2</v>
+        <v>49.4</v>
       </c>
       <c r="G29" s="147">
         <v>59.7</v>
@@ -43458,7 +43458,7 @@
       </c>
       <c r="E30" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>55.800000000000004</v>
+        <v>55.300000000000004</v>
       </c>
       <c r="G30" s="147">
         <v>63.5</v>
@@ -43473,7 +43473,7 @@
       </c>
       <c r="E31" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>75.900000000000006</v>
+        <v>74.600000000000009</v>
       </c>
       <c r="G31" s="147">
         <v>81.7</v>
@@ -43488,7 +43488,7 @@
       </c>
       <c r="E32" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>82.800000000000011</v>
+        <v>80.300000000000011</v>
       </c>
       <c r="G32" s="147">
         <v>90.9</v>
@@ -43503,7 +43503,7 @@
       </c>
       <c r="E33" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>170.39999999999998</v>
+        <v>167.7</v>
       </c>
       <c r="G33" s="147">
         <v>177.2</v>
@@ -43518,7 +43518,7 @@
       </c>
       <c r="E34" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>255.00000000000006</v>
+        <v>258.30000000000007</v>
       </c>
       <c r="G34" s="147">
         <v>263.10000000000002</v>
@@ -43533,7 +43533,7 @@
       </c>
       <c r="E35" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>102.19999999999999</v>
+        <v>100.6</v>
       </c>
       <c r="G35" s="147">
         <v>110.6</v>
@@ -43548,7 +43548,7 @@
       </c>
       <c r="E36" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>71.2</v>
+        <v>71</v>
       </c>
       <c r="G36" s="147">
         <v>82.3</v>
@@ -43563,7 +43563,7 @@
       </c>
       <c r="E37" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>70.400000000000006</v>
+        <v>68.5</v>
       </c>
       <c r="G37" s="147">
         <v>78.400000000000006</v>
@@ -43578,7 +43578,7 @@
       </c>
       <c r="E38" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>90.2</v>
+        <v>87.3</v>
       </c>
       <c r="G38" s="147">
         <v>96.3</v>
@@ -43593,7 +43593,7 @@
       </c>
       <c r="E39" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>45.8</v>
+        <v>45.3</v>
       </c>
       <c r="G39" s="147">
         <v>54.8</v>
@@ -43608,7 +43608,7 @@
       </c>
       <c r="E40" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>42.6</v>
+        <v>40.800000000000004</v>
       </c>
       <c r="G40" s="147">
         <v>49.9</v>
@@ -43623,7 +43623,7 @@
       </c>
       <c r="E41" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>218.7</v>
+        <v>216.2</v>
       </c>
       <c r="G41" s="147">
         <v>226.1</v>
@@ -43638,7 +43638,7 @@
       </c>
       <c r="E42" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>114.7</v>
+        <v>117.2</v>
       </c>
       <c r="G42" s="147">
         <v>125</v>
@@ -43653,7 +43653,7 @@
       </c>
       <c r="E43" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>51.3</v>
+        <v>49.5</v>
       </c>
       <c r="G43" s="147">
         <v>56.7</v>
@@ -43668,7 +43668,7 @@
       </c>
       <c r="E44" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>184.3</v>
+        <v>182.4</v>
       </c>
       <c r="G44" s="147">
         <v>191.3</v>
@@ -43683,7 +43683,7 @@
       </c>
       <c r="E45" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>62.2</v>
+        <v>61.4</v>
       </c>
       <c r="G45" s="147">
         <v>68.2</v>
@@ -43698,7 +43698,7 @@
       </c>
       <c r="E46" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="G46" s="147">
         <v>56.8</v>
@@ -43713,7 +43713,7 @@
       </c>
       <c r="E47" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>89.999999999999986</v>
+        <v>90.3</v>
       </c>
       <c r="G47" s="147">
         <v>97.6</v>
@@ -43728,7 +43728,7 @@
       </c>
       <c r="E48" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>47.599999999999994</v>
+        <v>44.9</v>
       </c>
       <c r="G48" s="147">
         <v>54.8</v>
@@ -43743,7 +43743,7 @@
       </c>
       <c r="E49" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>43.500000000000007</v>
+        <v>45.500000000000007</v>
       </c>
       <c r="G49" s="147">
         <v>54.7</v>
@@ -43758,7 +43758,7 @@
       </c>
       <c r="E50" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>46.8</v>
+        <v>46.1</v>
       </c>
       <c r="G50" s="147">
         <v>54.7</v>
@@ -43773,7 +43773,7 @@
       </c>
       <c r="E51" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>33.4</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="G51" s="147">
         <v>41.6</v>
@@ -43788,7 +43788,7 @@
       </c>
       <c r="E52" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>22.2</v>
+        <v>25.400000000000002</v>
       </c>
       <c r="G52" s="147">
         <v>30.5</v>
@@ -43803,7 +43803,7 @@
       </c>
       <c r="E53" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>43.3</v>
+        <v>41.5</v>
       </c>
       <c r="G53" s="147">
         <v>50</v>
@@ -43818,7 +43818,7 @@
       </c>
       <c r="E54" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>34.5</v>
+        <v>35.1</v>
       </c>
       <c r="G54" s="147">
         <v>42.1</v>
@@ -43833,7 +43833,7 @@
       </c>
       <c r="E55" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>11.999999999999998</v>
+        <v>10.299999999999999</v>
       </c>
       <c r="G55" s="147">
         <v>19.7</v>
@@ -43848,7 +43848,7 @@
       </c>
       <c r="E56" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>19.2</v>
+        <v>20.8</v>
       </c>
       <c r="G56" s="147">
         <v>26.5</v>
@@ -43863,7 +43863,7 @@
       </c>
       <c r="E57" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>40.9</v>
+        <v>39.9</v>
       </c>
       <c r="G57" s="147">
         <v>48.4</v>
@@ -43878,7 +43878,7 @@
       </c>
       <c r="E58" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>39.799999999999997</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="G58" s="147">
         <v>45.9</v>
@@ -43893,7 +43893,7 @@
       </c>
       <c r="E59" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>37.599999999999994</v>
+        <v>34.5</v>
       </c>
       <c r="G59" s="147">
         <v>45</v>
@@ -43908,7 +43908,7 @@
       </c>
       <c r="E60" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>59.400000000000006</v>
+        <v>56.900000000000006</v>
       </c>
       <c r="G60" s="147">
         <v>67.2</v>
@@ -43923,7 +43923,7 @@
       </c>
       <c r="E61" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>196.60000000000002</v>
+        <v>197.60000000000002</v>
       </c>
       <c r="G61" s="147">
         <v>203.8</v>
@@ -43938,7 +43938,7 @@
       </c>
       <c r="E62" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>30.1</v>
+        <v>31.2</v>
       </c>
       <c r="G62" s="147">
         <v>37.1</v>
@@ -43953,7 +43953,7 @@
       </c>
       <c r="E63" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>103.3</v>
+        <v>104.39999999999999</v>
       </c>
       <c r="G63" s="158">
         <v>112.1</v>
@@ -43968,7 +43968,7 @@
       </c>
       <c r="E64" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>46.300000000000004</v>
+        <v>44.5</v>
       </c>
       <c r="G64" s="149">
         <v>55</v>
@@ -43983,7 +43983,7 @@
       </c>
       <c r="E65" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="G65" s="149">
         <v>37.700000000000003</v>
@@ -43998,7 +43998,7 @@
       </c>
       <c r="E66" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="G66" s="149">
         <v>19.600000000000001</v>
@@ -44013,7 +44013,7 @@
       </c>
       <c r="E67" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>82.199999999999989</v>
+        <v>81.5</v>
       </c>
       <c r="G67" s="149">
         <v>90</v>
@@ -44028,7 +44028,7 @@
       </c>
       <c r="E68" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>31.800000000000004</v>
+        <v>34.5</v>
       </c>
       <c r="G68" s="150">
         <v>40.200000000000003</v>
@@ -44043,7 +44043,7 @@
       </c>
       <c r="E69" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>76.7</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="G69" s="150">
         <v>88.5</v>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="E70" s="157">
         <f t="shared" ref="E70:E85" ca="1" si="1">B70-RANDBETWEEN(2, 5)-RANDBETWEEN(1,10)/10</f>
-        <v>75.2</v>
+        <v>77.8</v>
       </c>
       <c r="G70" s="150">
         <v>84.2</v>
@@ -44073,7 +44073,7 @@
       </c>
       <c r="E71" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>85.500000000000014</v>
+        <v>84.100000000000009</v>
       </c>
       <c r="G71" s="149">
         <v>92.9</v>
@@ -44088,7 +44088,7 @@
       </c>
       <c r="E72" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>59.100000000000009</v>
+        <v>57.500000000000007</v>
       </c>
       <c r="G72" s="149">
         <v>67.400000000000006</v>
@@ -44103,7 +44103,7 @@
       </c>
       <c r="E73" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>14.500000000000002</v>
+        <v>15.900000000000002</v>
       </c>
       <c r="G73" s="149">
         <v>21.5</v>
@@ -44118,7 +44118,7 @@
       </c>
       <c r="E74" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>30.800000000000004</v>
+        <v>32.300000000000004</v>
       </c>
       <c r="G74" s="149">
         <v>40.200000000000003</v>
@@ -44133,7 +44133,7 @@
       </c>
       <c r="E75" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>81.499999999999986</v>
+        <v>82.199999999999989</v>
       </c>
       <c r="G75" s="149">
         <v>89.1</v>
@@ -44148,7 +44148,7 @@
       </c>
       <c r="E76" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>74.900000000000006</v>
+        <v>76.2</v>
       </c>
       <c r="G76" s="149">
         <v>85.4</v>
@@ -44163,7 +44163,7 @@
       </c>
       <c r="E77" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>80.899999999999991</v>
+        <v>79.2</v>
       </c>
       <c r="G77" s="150">
         <v>89.5</v>
@@ -44178,7 +44178,7 @@
       </c>
       <c r="E78" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>27.9</v>
+        <v>31.299999999999997</v>
       </c>
       <c r="G78" s="150">
         <v>39.4</v>
@@ -44193,7 +44193,7 @@
       </c>
       <c r="E79" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>63</v>
+        <v>61.5</v>
       </c>
       <c r="G79" s="149">
         <v>68.2</v>
@@ -44208,7 +44208,7 @@
       </c>
       <c r="E80" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>97.8</v>
+        <v>95.2</v>
       </c>
       <c r="G80" s="149">
         <v>104</v>
@@ -44223,7 +44223,7 @@
       </c>
       <c r="E81" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>131.30000000000001</v>
+        <v>129.69999999999999</v>
       </c>
       <c r="G81" s="149">
         <v>137.9</v>
@@ -44238,7 +44238,7 @@
       </c>
       <c r="E82" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>137.5</v>
+        <v>138.19999999999999</v>
       </c>
       <c r="G82" s="149">
         <v>144</v>
@@ -44253,7 +44253,7 @@
       </c>
       <c r="E83" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>108.6</v>
+        <v>108.1</v>
       </c>
       <c r="G83" s="149">
         <v>115.3</v>
@@ -44268,7 +44268,7 @@
       </c>
       <c r="E84" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>29.9</v>
+        <v>32</v>
       </c>
       <c r="G84" s="150">
         <v>40.1</v>
@@ -44283,7 +44283,7 @@
       </c>
       <c r="E85" s="157">
         <f t="shared" ca="1" si="1"/>
-        <v>122.60000000000001</v>
+        <v>120.30000000000001</v>
       </c>
       <c r="G85" s="150">
         <v>128.30000000000001</v>
@@ -44345,7 +44345,7 @@
       </c>
       <c r="E5" s="157">
         <f ca="1">B5-RANDBETWEEN(2, 5)-RANDBETWEEN(1,10)/10</f>
-        <v>75.900000000000006</v>
+        <v>77.2</v>
       </c>
       <c r="F5" s="157"/>
       <c r="G5" s="147">
@@ -44361,7 +44361,7 @@
       </c>
       <c r="E6" s="157">
         <f t="shared" ref="E6:E61" ca="1" si="0">B6-RANDBETWEEN(2, 5)-RANDBETWEEN(1,10)/10</f>
-        <v>102.3</v>
+        <v>106</v>
       </c>
       <c r="G6" s="147">
         <v>114</v>
@@ -44376,7 +44376,7 @@
       </c>
       <c r="E7" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>122.80000000000001</v>
+        <v>123.90000000000002</v>
       </c>
       <c r="G7" s="147">
         <v>132.80000000000001</v>
@@ -44391,7 +44391,7 @@
       </c>
       <c r="E8" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>88.9</v>
+        <v>86.6</v>
       </c>
       <c r="G8" s="147">
         <v>96.2</v>
@@ -44406,7 +44406,7 @@
       </c>
       <c r="E9" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>102.10000000000001</v>
+        <v>100.80000000000001</v>
       </c>
       <c r="G9" s="147">
         <v>111.9</v>
@@ -44421,7 +44421,7 @@
       </c>
       <c r="E10" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>101.4</v>
+        <v>98.6</v>
       </c>
       <c r="G10" s="147">
         <v>110</v>
@@ -44436,7 +44436,7 @@
       </c>
       <c r="E11" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>98.1</v>
+        <v>98.8</v>
       </c>
       <c r="G11" s="147">
         <v>107.7</v>
@@ -44451,7 +44451,7 @@
       </c>
       <c r="E12" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>101.2</v>
+        <v>101.89999999999999</v>
       </c>
       <c r="G12" s="147">
         <v>108.3</v>
@@ -44466,7 +44466,7 @@
       </c>
       <c r="E13" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>169</v>
+        <v>168.5</v>
       </c>
       <c r="G13" s="147">
         <v>176.5</v>
@@ -44481,7 +44481,7 @@
       </c>
       <c r="E14" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>28.2</v>
+        <v>30.4</v>
       </c>
       <c r="G14" s="147">
         <v>36.299999999999997</v>
@@ -44496,7 +44496,7 @@
       </c>
       <c r="E15" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>43.6</v>
+        <v>45</v>
       </c>
       <c r="G15" s="147">
         <v>53.5</v>
@@ -44511,7 +44511,7 @@
       </c>
       <c r="E16" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>70.400000000000006</v>
+        <v>71.300000000000011</v>
       </c>
       <c r="G16" s="147">
         <v>78.900000000000006</v>
@@ -44526,7 +44526,7 @@
       </c>
       <c r="E17" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>46.699999999999996</v>
+        <v>45.9</v>
       </c>
       <c r="G17" s="147">
         <v>53.6</v>
@@ -44541,7 +44541,7 @@
       </c>
       <c r="E18" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>28.799999999999997</v>
+        <v>29.199999999999996</v>
       </c>
       <c r="G18" s="147">
         <v>38.799999999999997</v>
@@ -44556,7 +44556,7 @@
       </c>
       <c r="E19" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>76.299999999999983</v>
+        <v>75.799999999999983</v>
       </c>
       <c r="G19" s="147">
         <v>82.6</v>
@@ -44571,7 +44571,7 @@
       </c>
       <c r="E20" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>34.099999999999994</v>
+        <v>30.299999999999997</v>
       </c>
       <c r="G20" s="147">
         <v>40.799999999999997</v>
@@ -44586,7 +44586,7 @@
       </c>
       <c r="E21" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>45.8</v>
+        <v>45.4</v>
       </c>
       <c r="G21" s="147">
         <v>52.9</v>
@@ -44601,7 +44601,7 @@
       </c>
       <c r="E22" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>77.399999999999991</v>
+        <v>76.899999999999991</v>
       </c>
       <c r="G22" s="147">
         <v>83.8</v>
@@ -44616,7 +44616,7 @@
       </c>
       <c r="E23" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>587.70000000000005</v>
+        <v>587.20000000000005</v>
       </c>
       <c r="G23" s="147">
         <v>596.4</v>
@@ -44631,7 +44631,7 @@
       </c>
       <c r="E24" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>98.699999999999989</v>
+        <v>98.399999999999991</v>
       </c>
       <c r="G24" s="147">
         <v>107.3</v>
@@ -44646,7 +44646,7 @@
       </c>
       <c r="E25" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>45.8</v>
+        <v>45.2</v>
       </c>
       <c r="G25" s="147">
         <v>51.7</v>
@@ -44661,7 +44661,7 @@
       </c>
       <c r="E26" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>29.800000000000004</v>
+        <v>28.400000000000002</v>
       </c>
       <c r="G26" s="147">
         <v>36.700000000000003</v>
@@ -44676,7 +44676,7 @@
       </c>
       <c r="E27" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>41.400000000000006</v>
+        <v>43.2</v>
       </c>
       <c r="G27" s="147">
         <v>51.6</v>
@@ -44691,7 +44691,7 @@
       </c>
       <c r="E28" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>72.399999999999991</v>
+        <v>71.499999999999986</v>
       </c>
       <c r="G28" s="147">
         <v>79.599999999999994</v>
@@ -44706,7 +44706,7 @@
       </c>
       <c r="E29" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>71.699999999999989</v>
+        <v>70.3</v>
       </c>
       <c r="G29" s="147">
         <v>79.3</v>
@@ -44721,7 +44721,7 @@
       </c>
       <c r="E30" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>24.7</v>
+        <v>23.299999999999997</v>
       </c>
       <c r="G30" s="147">
         <v>34.4</v>
@@ -44736,7 +44736,7 @@
       </c>
       <c r="E31" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>39.199999999999996</v>
+        <v>38</v>
       </c>
       <c r="G31" s="147">
         <v>46.9</v>
@@ -44751,7 +44751,7 @@
       </c>
       <c r="E32" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>282.8</v>
+        <v>282.09999999999997</v>
       </c>
       <c r="G32" s="147">
         <v>292.2</v>
@@ -44766,7 +44766,7 @@
       </c>
       <c r="E33" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>260.79999999999995</v>
+        <v>263.29999999999995</v>
       </c>
       <c r="G33" s="147">
         <v>268.7</v>
@@ -44781,7 +44781,7 @@
       </c>
       <c r="E34" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>74.2</v>
+        <v>71.7</v>
       </c>
       <c r="G34" s="147">
         <v>78.7</v>
@@ -44796,7 +44796,7 @@
       </c>
       <c r="E35" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>75.599999999999994</v>
+        <v>75.7</v>
       </c>
       <c r="G35" s="147">
         <v>84</v>
@@ -44811,7 +44811,7 @@
       </c>
       <c r="E36" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="G36" s="147">
         <v>54.3</v>
@@ -44826,7 +44826,7 @@
       </c>
       <c r="E37" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>72.599999999999994</v>
+        <v>74.5</v>
       </c>
       <c r="G37" s="147">
         <v>82.1</v>
@@ -44841,7 +44841,7 @@
       </c>
       <c r="E38" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>89.2</v>
+        <v>89.800000000000011</v>
       </c>
       <c r="G38" s="147">
         <v>98.7</v>
@@ -44856,7 +44856,7 @@
       </c>
       <c r="E39" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>38.4</v>
+        <v>37.1</v>
       </c>
       <c r="G39" s="147">
         <v>47.6</v>
@@ -44871,7 +44871,7 @@
       </c>
       <c r="E40" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>75.7</v>
+        <v>75.2</v>
       </c>
       <c r="G40" s="147">
         <v>83.9</v>
@@ -44886,7 +44886,7 @@
       </c>
       <c r="E41" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>32.200000000000003</v>
+        <v>30</v>
       </c>
       <c r="G41" s="150">
         <v>39.700000000000003</v>
@@ -44901,7 +44901,7 @@
       </c>
       <c r="E42" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>80.599999999999994</v>
+        <v>82.3</v>
       </c>
       <c r="G42" s="147">
         <v>87.8</v>
@@ -44916,7 +44916,7 @@
       </c>
       <c r="E43" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>73.7</v>
+        <v>72.7</v>
       </c>
       <c r="G43" s="147">
         <v>80.900000000000006</v>
@@ -44931,7 +44931,7 @@
       </c>
       <c r="E44" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>82.100000000000009</v>
+        <v>85.300000000000011</v>
       </c>
       <c r="G44" s="147">
         <v>90.9</v>
@@ -44946,7 +44946,7 @@
       </c>
       <c r="E45" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>74.099999999999994</v>
+        <v>71.699999999999989</v>
       </c>
       <c r="G45" s="147">
         <v>81.8</v>
@@ -44961,7 +44961,7 @@
       </c>
       <c r="E46" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>31.400000000000002</v>
+        <v>32</v>
       </c>
       <c r="G46" s="147">
         <v>39.700000000000003</v>
@@ -44976,7 +44976,7 @@
       </c>
       <c r="E47" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>74.2</v>
+        <v>72</v>
       </c>
       <c r="G47" s="147">
         <v>80.8</v>
@@ -44991,7 +44991,7 @@
       </c>
       <c r="E48" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>79</v>
+        <v>80.5</v>
       </c>
       <c r="G48" s="147">
         <v>86.8</v>
@@ -45006,7 +45006,7 @@
       </c>
       <c r="E49" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>78.7</v>
+        <v>81</v>
       </c>
       <c r="G49" s="147">
         <v>87.7</v>
@@ -45021,7 +45021,7 @@
       </c>
       <c r="E50" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>106.89999999999999</v>
+        <v>105.5</v>
       </c>
       <c r="G50" s="147">
         <v>112.1</v>
@@ -45036,7 +45036,7 @@
       </c>
       <c r="E51" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>34.899999999999991</v>
+        <v>34.999999999999993</v>
       </c>
       <c r="G51" s="147">
         <v>41.3</v>
@@ -45051,7 +45051,7 @@
       </c>
       <c r="E52" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>93.4</v>
+        <v>93.7</v>
       </c>
       <c r="G52" s="147">
         <v>102</v>
@@ -45066,7 +45066,7 @@
       </c>
       <c r="E53" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>32.900000000000006</v>
+        <v>32.800000000000004</v>
       </c>
       <c r="G53" s="147">
         <v>40.200000000000003</v>
@@ -45081,7 +45081,7 @@
       </c>
       <c r="E54" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>79.599999999999994</v>
+        <v>79.399999999999991</v>
       </c>
       <c r="G54" s="149">
         <v>88.6</v>
@@ -45096,7 +45096,7 @@
       </c>
       <c r="E55" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>30.9</v>
+        <v>31.5</v>
       </c>
       <c r="G55" s="149">
         <v>39.799999999999997</v>
@@ -45111,7 +45111,7 @@
       </c>
       <c r="E56" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>28.799999999999997</v>
+        <v>28.399999999999995</v>
       </c>
       <c r="G56" s="149">
         <v>38.9</v>
@@ -45126,7 +45126,7 @@
       </c>
       <c r="E57" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>97.1</v>
+        <v>97.199999999999989</v>
       </c>
       <c r="G57" s="149">
         <v>104</v>
@@ -45141,7 +45141,7 @@
       </c>
       <c r="E58" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>32.4</v>
+        <v>31.400000000000002</v>
       </c>
       <c r="G58" s="149">
         <v>38.9</v>
@@ -45156,7 +45156,7 @@
       </c>
       <c r="E59" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>135.4</v>
+        <v>137.5</v>
       </c>
       <c r="G59" s="149">
         <v>147</v>
@@ -45171,7 +45171,7 @@
       </c>
       <c r="E60" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>74.5</v>
       </c>
       <c r="G60" s="152">
         <v>83.5</v>
@@ -45186,7 +45186,7 @@
       </c>
       <c r="E61" s="157">
         <f t="shared" ca="1" si="0"/>
-        <v>107.7</v>
+        <v>107.2</v>
       </c>
       <c r="G61" s="150">
         <v>116</v>
